--- a/automation_framework_DemowebShop/src/test/resources/testdata.xlsx
+++ b/automation_framework_DemowebShop/src/test/resources/testdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\eclipse-workspace\automation_framework_DemowebShop\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\git\repository_DemoWebShop\automation_framework_DemowebShop\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E53BCA-1C3F-477E-AE5F-8C42199B87D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C957CE-2CB9-425E-B78F-DB7030FAE73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="registerdata" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="emptfield" sheetId="9" r:id="rId9"/>
     <sheet name="usedmail" sheetId="10" r:id="rId10"/>
     <sheet name="wrongmail" sheetId="11" r:id="rId11"/>
+    <sheet name="billaddress" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>gender</t>
   </si>
@@ -247,7 +248,16 @@
     <t>muthu12</t>
   </si>
   <si>
-    <t>muthu987@gmail.com</t>
+    <t>muthu9875@gmail.com</t>
+  </si>
+  <si>
+    <t>zipcode</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>14, kodambakkam</t>
   </si>
 </sst>
 </file>
@@ -990,6 +1000,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7340CFB5-1AFB-4664-B365-F30E78CD3ED4}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2">
+        <v>600029</v>
+      </c>
+      <c r="D2">
+        <v>2345678910</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3322DD1B-6F43-4342-9F08-D62DAB50EFD6}">
   <dimension ref="A1:F2"/>
